--- a/data.xlsx
+++ b/data.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\lolm\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF8C47A-F980-4F75-8E2A-BFED8E23A278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="符文大乱斗英雄属性调整" sheetId="1" r:id="rId1"/>
@@ -13,24 +19,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">符文大乱斗英雄属性调整!$B$1:$B$143</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="224">
   <si>
     <t>英雄联盟手游符文大乱斗英雄属性调整表</t>
   </si>
@@ -673,19 +666,45 @@
   </si>
   <si>
     <t>阿卡丽</t>
+  </si>
+  <si>
+    <t>备注3</t>
+  </si>
+  <si>
+    <t>受到伤害：100% &gt;&gt;&gt; 95%，造成伤害：90% &gt;&gt;&gt; 100%，7.3版本</t>
+  </si>
+  <si>
+    <t>造成伤害：100% &gt;&gt;&gt; 110%，受到伤害：100% &gt;&gt;&gt; 90%，7.3版本</t>
+  </si>
+  <si>
+    <t>受到伤害：100% &gt;&gt;&gt; 95%，7.3版本</t>
+  </si>
+  <si>
+    <t>造成伤害：110% &gt;&gt;&gt; 115%，受到伤害：80% &gt;&gt;&gt; 75%，7.3版本</t>
+  </si>
+  <si>
+    <t>受到伤害：100% &gt;&gt;&gt; 90%，7.3版本</t>
+  </si>
+  <si>
+    <t>受到伤害：90% &gt;&gt;&gt; 80%，7.3版本</t>
+  </si>
+  <si>
+    <t>造成伤害：105% &gt;&gt;&gt; 110%，受到伤害：90% &gt;&gt;&gt; 85%，7.3版本</t>
+  </si>
+  <si>
+    <t>彗</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>法师</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -710,7 +729,7 @@
       <sz val="10"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -723,7 +742,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -738,151 +757,36 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -927,192 +831,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1146,264 +870,26 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FFBFBFBF"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1442,82 +928,62 @@
     <xf numFmtId="9" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1533,11 +999,17 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 2" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1" cstate="print"/>
+        <xdr:cNvPr id="3" name="Image 2" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1572,13 +1044,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1025" name="Image 105" descr="Picture"/>
+        <xdr:cNvPr id="1025" name="Image 105" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -1615,13 +1093,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1026" name="Image 98" descr="Picture"/>
+        <xdr:cNvPr id="1026" name="Image 98" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -1658,13 +1142,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="164" name="图片 163"/>
+        <xdr:cNvPr id="164" name="图片 163">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A4000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -1701,13 +1191,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="165" name="图片 164"/>
+        <xdr:cNvPr id="165" name="图片 164">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A5000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId5" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -1744,13 +1240,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="167" name="图片 166"/>
+        <xdr:cNvPr id="167" name="图片 166">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A7000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId6" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -1787,13 +1289,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="168" name="图片 167"/>
+        <xdr:cNvPr id="168" name="图片 167">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A8000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId7" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -1830,13 +1338,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="169" name="图片 168"/>
+        <xdr:cNvPr id="169" name="图片 168">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A9000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId8" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -1873,13 +1387,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="170" name="图片 169"/>
+        <xdr:cNvPr id="170" name="图片 169">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AA000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId9" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -1916,13 +1436,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="171" name="图片 170"/>
+        <xdr:cNvPr id="171" name="图片 170">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AB000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId10" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -1954,11 +1480,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Image 3" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId11" cstate="print"/>
+        <xdr:cNvPr id="4" name="Image 3" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1988,11 +1520,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Image 4" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId12" cstate="print"/>
+        <xdr:cNvPr id="5" name="Image 4" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2022,11 +1560,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Image 5" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId13" cstate="print"/>
+        <xdr:cNvPr id="6" name="Image 5" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2056,11 +1600,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Image 6" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId14" cstate="print"/>
+        <xdr:cNvPr id="7" name="Image 6" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2090,11 +1640,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Image 7" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId15" cstate="print"/>
+        <xdr:cNvPr id="8" name="Image 7" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2124,11 +1680,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Image 8" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId16" cstate="print"/>
+        <xdr:cNvPr id="9" name="Image 8" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2158,11 +1720,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Image 9" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId17" cstate="print"/>
+        <xdr:cNvPr id="10" name="Image 9" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2192,11 +1760,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Image 10" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId18" cstate="print"/>
+        <xdr:cNvPr id="11" name="Image 10" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2226,11 +1800,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Image 11" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId19" cstate="print"/>
+        <xdr:cNvPr id="12" name="Image 11" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2260,11 +1840,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Image 12" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId20" cstate="print"/>
+        <xdr:cNvPr id="13" name="Image 12" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2294,11 +1880,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Image 13" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId21" cstate="print"/>
+        <xdr:cNvPr id="14" name="Image 13" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2328,11 +1920,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Image 14" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId22" cstate="print"/>
+        <xdr:cNvPr id="15" name="Image 14" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2362,11 +1960,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Image 15" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId23" cstate="print"/>
+        <xdr:cNvPr id="16" name="Image 15" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2396,11 +2000,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Image 16" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId24" cstate="print"/>
+        <xdr:cNvPr id="17" name="Image 16" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2430,11 +2040,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Image 17" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId25" cstate="print"/>
+        <xdr:cNvPr id="18" name="Image 17" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2464,11 +2080,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Image 18" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId26" cstate="print"/>
+        <xdr:cNvPr id="19" name="Image 18" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2498,11 +2120,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Image 19" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId27" cstate="print"/>
+        <xdr:cNvPr id="20" name="Image 19" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2532,11 +2160,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Image 20" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId28" cstate="print"/>
+        <xdr:cNvPr id="21" name="Image 20" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2566,11 +2200,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Image 21" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId29" cstate="print"/>
+        <xdr:cNvPr id="22" name="Image 21" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2600,11 +2240,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Image 22" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId30" cstate="print"/>
+        <xdr:cNvPr id="23" name="Image 22" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2634,11 +2280,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Image 23" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId31" cstate="print"/>
+        <xdr:cNvPr id="24" name="Image 23" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2668,11 +2320,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Image 24" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId32" cstate="print"/>
+        <xdr:cNvPr id="25" name="Image 24" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2702,11 +2360,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Image 25" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId33" cstate="print"/>
+        <xdr:cNvPr id="26" name="Image 25" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2736,11 +2400,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="Image 26" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId34" cstate="print"/>
+        <xdr:cNvPr id="27" name="Image 26" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2770,11 +2440,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Image 27" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId35" cstate="print"/>
+        <xdr:cNvPr id="28" name="Image 27" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2804,11 +2480,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="Image 28" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId36" cstate="print"/>
+        <xdr:cNvPr id="29" name="Image 28" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2838,11 +2520,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="Image 29" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId37" cstate="print"/>
+        <xdr:cNvPr id="30" name="Image 29" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2872,11 +2560,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="Image 30" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId38" cstate="print"/>
+        <xdr:cNvPr id="31" name="Image 30" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2906,11 +2600,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="Image 31" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId39" cstate="print"/>
+        <xdr:cNvPr id="32" name="Image 31" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2940,11 +2640,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="Image 32" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId40" cstate="print"/>
+        <xdr:cNvPr id="33" name="Image 32" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2974,11 +2680,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Image 33" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId41" cstate="print"/>
+        <xdr:cNvPr id="34" name="Image 33" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3008,11 +2720,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Image 34" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId42" cstate="print"/>
+        <xdr:cNvPr id="35" name="Image 34" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3042,11 +2760,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Image 35" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId43" cstate="print"/>
+        <xdr:cNvPr id="36" name="Image 35" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId43" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3076,11 +2800,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Image 36" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId44" cstate="print"/>
+        <xdr:cNvPr id="37" name="Image 36" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId44" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3110,11 +2840,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Image 37" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId45" cstate="print"/>
+        <xdr:cNvPr id="38" name="Image 37" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId45" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3144,11 +2880,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="Image 38" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId46" cstate="print"/>
+        <xdr:cNvPr id="39" name="Image 38" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3178,11 +2920,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="Image 39" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId47" cstate="print"/>
+        <xdr:cNvPr id="40" name="Image 39" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3212,11 +2960,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="41" name="Image 40" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId48" cstate="print"/>
+        <xdr:cNvPr id="41" name="Image 40" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId48" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3246,11 +3000,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="Image 41" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
+        <xdr:cNvPr id="42" name="Image 41" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId49" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3280,11 +3040,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="Image 42" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
+        <xdr:cNvPr id="43" name="Image 42" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3314,11 +3080,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Image 43" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId51" cstate="print"/>
+        <xdr:cNvPr id="44" name="Image 43" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId51" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3348,11 +3120,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Image 44" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId52" cstate="print"/>
+        <xdr:cNvPr id="45" name="Image 44" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId52" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3382,11 +3160,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Image 45" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId53" cstate="print"/>
+        <xdr:cNvPr id="46" name="Image 45" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId53" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3416,11 +3200,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Image 46" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId54" cstate="print"/>
+        <xdr:cNvPr id="47" name="Image 46" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId54" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3450,11 +3240,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Image 47" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId55" cstate="print"/>
+        <xdr:cNvPr id="48" name="Image 47" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId55" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3484,11 +3280,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Image 48" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId56" cstate="print"/>
+        <xdr:cNvPr id="49" name="Image 48" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId56" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3518,11 +3320,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Image 49" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId57" cstate="print"/>
+        <xdr:cNvPr id="50" name="Image 49" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId57" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3552,11 +3360,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Image 50" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId58" cstate="print"/>
+        <xdr:cNvPr id="51" name="Image 50" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId58" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3586,11 +3400,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Image 51" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId59" cstate="print"/>
+        <xdr:cNvPr id="52" name="Image 51" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId59" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3620,11 +3440,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Image 52" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId60" cstate="print"/>
+        <xdr:cNvPr id="53" name="Image 52" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId60" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3654,11 +3480,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Image 53" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId61" cstate="print"/>
+        <xdr:cNvPr id="54" name="Image 53" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId61" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3688,11 +3520,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Image 54" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId62" cstate="print"/>
+        <xdr:cNvPr id="55" name="Image 54" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId62" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3722,11 +3560,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Image 55" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId63" cstate="print"/>
+        <xdr:cNvPr id="56" name="Image 55" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId63" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3756,11 +3600,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Image 56" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId64" cstate="print"/>
+        <xdr:cNvPr id="57" name="Image 56" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId64" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3790,11 +3640,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Image 57" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId65" cstate="print"/>
+        <xdr:cNvPr id="58" name="Image 57" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId65" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3824,11 +3680,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Image 58" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId66" cstate="print"/>
+        <xdr:cNvPr id="59" name="Image 58" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId66" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3858,11 +3720,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Image 60" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId67" cstate="print"/>
+        <xdr:cNvPr id="61" name="Image 60" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId67" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3892,11 +3760,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Image 61" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId68" cstate="print"/>
+        <xdr:cNvPr id="62" name="Image 61" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId68" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3926,11 +3800,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Image 62" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId69" cstate="print"/>
+        <xdr:cNvPr id="63" name="Image 62" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId69" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3960,11 +3840,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Image 63" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId70" cstate="print"/>
+        <xdr:cNvPr id="64" name="Image 63" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId70" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3994,11 +3880,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Image 64" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId71" cstate="print"/>
+        <xdr:cNvPr id="65" name="Image 64" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId71" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4028,11 +3920,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Image 65" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId72" cstate="print"/>
+        <xdr:cNvPr id="66" name="Image 65" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId72" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4062,11 +3960,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Image 66" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId73" cstate="print"/>
+        <xdr:cNvPr id="67" name="Image 66" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId73" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4096,11 +4000,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Image 67" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId74" cstate="print"/>
+        <xdr:cNvPr id="68" name="Image 67" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId74" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4130,11 +4040,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Image 68" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId75" cstate="print"/>
+        <xdr:cNvPr id="69" name="Image 68" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId75" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4164,11 +4080,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Image 69" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId76" cstate="print"/>
+        <xdr:cNvPr id="70" name="Image 69" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId76" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4198,11 +4120,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Image 70" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId77" cstate="print"/>
+        <xdr:cNvPr id="71" name="Image 70" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId77" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4232,11 +4160,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Image 71" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId78" cstate="print"/>
+        <xdr:cNvPr id="72" name="Image 71" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId78" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4266,11 +4200,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Image 72" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId79" cstate="print"/>
+        <xdr:cNvPr id="73" name="Image 72" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId79" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4300,11 +4240,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Image 73" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId80" cstate="print"/>
+        <xdr:cNvPr id="74" name="Image 73" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId80" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4334,11 +4280,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Image 74" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId81" cstate="print"/>
+        <xdr:cNvPr id="75" name="Image 74" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId81" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4368,11 +4320,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Image 75" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId82" cstate="print"/>
+        <xdr:cNvPr id="76" name="Image 75" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId82" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4402,11 +4360,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Image 76" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId83" cstate="print"/>
+        <xdr:cNvPr id="77" name="Image 76" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId83" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4436,11 +4400,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Image 77" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId84" cstate="print"/>
+        <xdr:cNvPr id="78" name="Image 77" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId84" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4470,11 +4440,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Image 78" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId85" cstate="print"/>
+        <xdr:cNvPr id="79" name="Image 78" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId85" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4504,11 +4480,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Image 79" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId86" cstate="print"/>
+        <xdr:cNvPr id="80" name="Image 79" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId86" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4538,11 +4520,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Image 80" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId87" cstate="print"/>
+        <xdr:cNvPr id="81" name="Image 80" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId87" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4572,11 +4560,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Image 81" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId88" cstate="print"/>
+        <xdr:cNvPr id="82" name="Image 81" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId88" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4606,11 +4600,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Image 83" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId89" cstate="print"/>
+        <xdr:cNvPr id="84" name="Image 83" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId89" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4640,11 +4640,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Image 84" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId90" cstate="print"/>
+        <xdr:cNvPr id="85" name="Image 84" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId90" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4674,11 +4680,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Image 85" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId91" cstate="print"/>
+        <xdr:cNvPr id="86" name="Image 85" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId91" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4708,11 +4720,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Image 86" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId92" cstate="print"/>
+        <xdr:cNvPr id="87" name="Image 86" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId92" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4742,11 +4760,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Image 87" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId93" cstate="print"/>
+        <xdr:cNvPr id="88" name="Image 87" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId93" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4776,11 +4800,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Image 88" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId94" cstate="print"/>
+        <xdr:cNvPr id="89" name="Image 88" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId94" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4810,11 +4840,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Image 89" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId95" cstate="print"/>
+        <xdr:cNvPr id="90" name="Image 89" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId95" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4844,11 +4880,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Image 90" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId96" cstate="print"/>
+        <xdr:cNvPr id="91" name="Image 90" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId96" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4878,11 +4920,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Image 91" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId97" cstate="print"/>
+        <xdr:cNvPr id="92" name="Image 91" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId97" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4912,11 +4960,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Image 92" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId98" cstate="print"/>
+        <xdr:cNvPr id="93" name="Image 92" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId98" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4946,11 +5000,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Image 93" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId99" cstate="print"/>
+        <xdr:cNvPr id="94" name="Image 93" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId99" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4980,11 +5040,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Image 94" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId100" cstate="print"/>
+        <xdr:cNvPr id="95" name="Image 94" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId100" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5014,11 +5080,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Image 95" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId101" cstate="print"/>
+        <xdr:cNvPr id="96" name="Image 95" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId101" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5048,11 +5120,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Image 96" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId102" cstate="print"/>
+        <xdr:cNvPr id="97" name="Image 96" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId102" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5082,11 +5160,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Image 97" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId103" cstate="print"/>
+        <xdr:cNvPr id="98" name="Image 97" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId103" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5116,11 +5200,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Image 98" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId104" cstate="print"/>
+        <xdr:cNvPr id="99" name="Image 98" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId104" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5150,11 +5240,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Image 99" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId105" cstate="print"/>
+        <xdr:cNvPr id="100" name="Image 99" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId105" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5184,11 +5280,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Image 100" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId106" cstate="print"/>
+        <xdr:cNvPr id="101" name="Image 100" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId106" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5218,11 +5320,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Image 101" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId107" cstate="print"/>
+        <xdr:cNvPr id="102" name="Image 101" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId107" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5252,11 +5360,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Image 102" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId108" cstate="print"/>
+        <xdr:cNvPr id="103" name="Image 102" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId108" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5286,11 +5400,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Image 103" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId109" cstate="print"/>
+        <xdr:cNvPr id="104" name="Image 103" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId109" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5320,11 +5440,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Image 104" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId110" cstate="print"/>
+        <xdr:cNvPr id="105" name="Image 104" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId110" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5354,11 +5480,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Image 105" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId111" cstate="print"/>
+        <xdr:cNvPr id="106" name="Image 105" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId111" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5388,11 +5520,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Image 106" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId112" cstate="print"/>
+        <xdr:cNvPr id="107" name="Image 106" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId112" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5422,11 +5560,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Image 107" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId113" cstate="print"/>
+        <xdr:cNvPr id="108" name="Image 107" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId113" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5456,11 +5600,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Image 108" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId114" cstate="print"/>
+        <xdr:cNvPr id="109" name="Image 108" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId114" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5490,11 +5640,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Image 109" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId115" cstate="print"/>
+        <xdr:cNvPr id="110" name="Image 109" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId115" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5524,11 +5680,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Image 110" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId116" cstate="print"/>
+        <xdr:cNvPr id="111" name="Image 110" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId116" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5558,11 +5720,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Image 111" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId117" cstate="print"/>
+        <xdr:cNvPr id="112" name="Image 111" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId117" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5592,11 +5760,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Image 112" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId118" cstate="print"/>
+        <xdr:cNvPr id="113" name="Image 112" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId118" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5626,11 +5800,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Image 113" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId119" cstate="print"/>
+        <xdr:cNvPr id="114" name="Image 113" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId119" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5660,11 +5840,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Image 114" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId120" cstate="print"/>
+        <xdr:cNvPr id="115" name="Image 114" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId120" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5694,11 +5880,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Image 116" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId121" cstate="print"/>
+        <xdr:cNvPr id="117" name="Image 116" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId121" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5728,11 +5920,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Image 117" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId122" cstate="print"/>
+        <xdr:cNvPr id="118" name="Image 117" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId122" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5762,11 +5960,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Image 118" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId123" cstate="print"/>
+        <xdr:cNvPr id="119" name="Image 118" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId123" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5796,11 +6000,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Image 119" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId124" cstate="print"/>
+        <xdr:cNvPr id="120" name="Image 119" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId124" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5830,11 +6040,17 @@
     <xdr:ext cx="396240" cy="419100"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Image 120" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId125" cstate="print"/>
+        <xdr:cNvPr id="121" name="Image 120" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId125" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5864,11 +6080,17 @@
     <xdr:ext cx="381000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="122" name="Image 121" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId126" cstate="print"/>
+        <xdr:cNvPr id="122" name="Image 121" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId126" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5898,11 +6120,17 @@
     <xdr:ext cx="411480" cy="419100"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="124" name="Image 123" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId127" cstate="print"/>
+        <xdr:cNvPr id="124" name="Image 123" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId127" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5932,11 +6160,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="125" name="Image 124" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId128" cstate="print"/>
+        <xdr:cNvPr id="125" name="Image 124" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId128" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5966,11 +6200,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="127" name="Image 126" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId129" cstate="print"/>
+        <xdr:cNvPr id="127" name="Image 126" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId129" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6000,11 +6240,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="128" name="Image 127" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId130" cstate="print"/>
+        <xdr:cNvPr id="128" name="Image 127" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000080000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId130" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6034,11 +6280,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="129" name="Image 128" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId131" cstate="print"/>
+        <xdr:cNvPr id="129" name="Image 128" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000081000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId131" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6068,11 +6320,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="130" name="Image 129" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId132" cstate="print"/>
+        <xdr:cNvPr id="130" name="Image 129" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000082000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId132" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6102,11 +6360,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="131" name="Image 130" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId133" cstate="print"/>
+        <xdr:cNvPr id="131" name="Image 130" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000083000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId133" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6136,11 +6400,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="132" name="Image 131" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId134" cstate="print"/>
+        <xdr:cNvPr id="132" name="Image 131" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000084000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId134" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6170,11 +6440,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="133" name="Image 132" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId135" cstate="print"/>
+        <xdr:cNvPr id="133" name="Image 132" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000085000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId135" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6204,11 +6480,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="134" name="Image 133" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId136" cstate="print"/>
+        <xdr:cNvPr id="134" name="Image 133" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000086000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId136" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6238,11 +6520,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="135" name="Image 134" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId137" cstate="print"/>
+        <xdr:cNvPr id="135" name="Image 134" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000087000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId137" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6272,11 +6560,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="136" name="Image 135" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId138" cstate="print"/>
+        <xdr:cNvPr id="136" name="Image 135" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000088000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId138" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6306,11 +6600,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="137" name="Image 136" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId139" cstate="print"/>
+        <xdr:cNvPr id="137" name="Image 136" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000089000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId139" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6340,11 +6640,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="138" name="Image 137" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId140" cstate="print"/>
+        <xdr:cNvPr id="138" name="Image 137" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId140" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6374,11 +6680,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="139" name="Image 138" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId141" cstate="print"/>
+        <xdr:cNvPr id="139" name="Image 138" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId141" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6408,11 +6720,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="140" name="Image 139" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId142" cstate="print"/>
+        <xdr:cNvPr id="140" name="Image 139" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId142" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6442,11 +6760,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="141" name="Image 140" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId143" cstate="print"/>
+        <xdr:cNvPr id="141" name="Image 140" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId143" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6476,11 +6800,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="142" name="Image 141" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId144" cstate="print"/>
+        <xdr:cNvPr id="142" name="Image 141" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId144" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6510,11 +6840,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="143" name="Image 142" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId145" cstate="print"/>
+        <xdr:cNvPr id="143" name="Image 142" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId145" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6544,11 +6880,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="144" name="Image 143" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId146" cstate="print"/>
+        <xdr:cNvPr id="144" name="Image 143" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000090000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId146" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6578,11 +6920,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="145" name="Image 144" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId147" cstate="print"/>
+        <xdr:cNvPr id="145" name="Image 144" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000091000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId147" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6612,11 +6960,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="146" name="Image 145" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId148" cstate="print"/>
+        <xdr:cNvPr id="146" name="Image 145" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000092000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId148" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6646,11 +7000,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="147" name="Image 146" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId149" cstate="print"/>
+        <xdr:cNvPr id="147" name="Image 146" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000093000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId149" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6680,11 +7040,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="148" name="Image 147" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId150" cstate="print"/>
+        <xdr:cNvPr id="148" name="Image 147" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000094000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId150" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6714,11 +7080,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="149" name="Image 148" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId151" cstate="print"/>
+        <xdr:cNvPr id="149" name="Image 148" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000095000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId151" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6748,11 +7120,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="150" name="Image 149" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId152" cstate="print"/>
+        <xdr:cNvPr id="150" name="Image 149" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000096000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId152" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6782,11 +7160,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="151" name="Image 150" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId153" cstate="print"/>
+        <xdr:cNvPr id="151" name="Image 150" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000097000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId153" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6816,11 +7200,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="152" name="Image 151" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId154" cstate="print"/>
+        <xdr:cNvPr id="152" name="Image 151" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000098000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId154" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6850,11 +7240,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="153" name="Image 152" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId155" cstate="print"/>
+        <xdr:cNvPr id="153" name="Image 152" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000099000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId155" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6884,11 +7280,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="154" name="Image 153" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId156" cstate="print"/>
+        <xdr:cNvPr id="154" name="Image 153" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId156" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6918,11 +7320,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="155" name="Image 154" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId157" cstate="print"/>
+        <xdr:cNvPr id="155" name="Image 154" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId157" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6952,11 +7360,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="156" name="Image 155" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId158" cstate="print"/>
+        <xdr:cNvPr id="156" name="Image 155" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId158" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6986,11 +7400,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="157" name="Image 156" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId159" cstate="print"/>
+        <xdr:cNvPr id="157" name="Image 156" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId159" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7020,11 +7440,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="158" name="Image 157" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId160" cstate="print"/>
+        <xdr:cNvPr id="158" name="Image 157" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId160" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7054,11 +7480,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="159" name="Image 158" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId161" cstate="print"/>
+        <xdr:cNvPr id="159" name="Image 158" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId161" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7088,11 +7520,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="160" name="Image 159" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId162" cstate="print"/>
+        <xdr:cNvPr id="160" name="Image 159" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A0000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId162" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7122,11 +7560,17 @@
     <xdr:ext cx="381600" cy="381600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="161" name="Image 160" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId163" cstate="print"/>
+        <xdr:cNvPr id="161" name="Image 160" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A1000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId163" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7401,2740 +7845,2776 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J171"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.8"/>
+  <dimension ref="A1:K171"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
     <col min="2" max="2" width="18" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.1111111111111" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="1" customWidth="1"/>
     <col min="5" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="76.5555555555556" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.8888888888889" customWidth="1"/>
+    <col min="7" max="7" width="24.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
     <col min="9" max="9" width="36" customWidth="1"/>
-    <col min="10" max="10" width="53.1111111111111" style="1" customWidth="1"/>
+    <col min="10" max="10" width="34.21875" style="24" customWidth="1"/>
+    <col min="11" max="11" width="47" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.2" customHeight="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:11" ht="46.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="J1"/>
-    </row>
-    <row r="2" ht="40.05" customHeight="1" spans="1:10">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="J1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A3" s="6"/>
-      <c r="B3" s="7" t="s">
+      <c r="K2" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="5">
         <v>1</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="5">
         <v>1</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="5">
         <v>1.2</v>
       </c>
-      <c r="F3" s="8"/>
+      <c r="F3" s="5"/>
       <c r="G3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A4" s="6"/>
-      <c r="B4" s="10" t="s">
+    <row r="4" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="8">
         <v>1.05</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="8">
         <v>0.9</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="H4" s="9" t="s">
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="H4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7" t="s">
+    <row r="5" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="11">
-        <v>1.15</v>
-      </c>
-      <c r="D5" s="8">
+      <c r="C5" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D5" s="5">
         <v>0.85</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="5">
         <v>1.2</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="H5" s="9" t="s">
+      <c r="F5" s="5"/>
+      <c r="H5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A6" s="6"/>
-      <c r="B6" s="10" t="s">
+    <row r="6" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="12">
-        <v>1.15</v>
-      </c>
-      <c r="D6" s="11">
+      <c r="C6" s="9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D6" s="8">
         <v>0.75</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
       <c r="G6" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I6" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7" t="s">
+    <row r="7" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="11">
-        <v>1.15</v>
-      </c>
-      <c r="D7" s="13">
-        <v>1.15</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="H7" s="9" t="s">
+      <c r="C7" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="H7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A8" s="6"/>
-      <c r="B8" s="10" t="s">
+    <row r="8" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="11">
-        <v>1.15</v>
-      </c>
-      <c r="D8" s="12">
+      <c r="C8" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D8" s="9">
         <v>0.8</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="H8" s="9" t="s">
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="H8" s="6" t="s">
         <v>19</v>
       </c>
       <c r="I8" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B9" s="7" t="s">
+    <row r="9" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="11">
-        <v>1.1</v>
-      </c>
-      <c r="D9" s="8">
+      <c r="C9" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D9" s="5">
         <v>0.9</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="H9" s="9" t="s">
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="H9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B10" s="10" t="s">
+    <row r="10" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="12">
-        <v>1.1</v>
-      </c>
-      <c r="D10" s="11">
+      <c r="C10" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D10" s="8">
         <v>0.85</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
       <c r="G10" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I10" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B11" s="7" t="s">
+    <row r="11" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="5">
         <v>1</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="8">
         <v>0.85</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
       <c r="G11" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I11" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A12" s="6"/>
-      <c r="B12" s="10" t="s">
+    <row r="12" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="11">
-        <v>1.15</v>
-      </c>
-      <c r="D12" s="12">
+      <c r="C12" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D12" s="9">
         <v>0.8</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="9">
         <v>1.2</v>
       </c>
-      <c r="F12" s="12"/>
-      <c r="H12" s="9" t="s">
+      <c r="F12" s="9"/>
+      <c r="H12" s="6" t="s">
         <v>19</v>
       </c>
       <c r="I12" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B13" s="7" t="s">
+    <row r="13" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="8">
         <v>1.05</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="5">
         <v>0.95</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
       <c r="G13" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="6" t="s">
         <v>19</v>
       </c>
       <c r="I13" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B14" s="10" t="s">
+    <row r="14" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="9">
         <v>1</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="8">
         <v>0.9</v>
       </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="H14" s="9" t="s">
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="H14" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="J14" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B15" s="7" t="s">
+    <row r="15" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="5">
         <v>1</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="8">
         <v>0.9</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="H15" s="9" t="s">
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="H15" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B16" s="10" t="s">
+    <row r="16" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="8">
         <v>1.05</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="8">
         <v>0.9</v>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="H16" s="9" t="s">
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="H16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="J16" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B17" s="7" t="s">
+    <row r="17" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="8">
         <v>1.2</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="5">
         <v>1</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="H17" s="9" t="s">
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="H17" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B18" s="10" t="s">
+    <row r="18" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="9">
         <v>1</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="9">
         <v>1</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="14" t="s">
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B19" s="7" t="s">
+    <row r="19" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="5">
         <v>1</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="5">
         <v>1</v>
       </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="H19" s="9" t="s">
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="H19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="20" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B20" s="10" t="s">
+    <row r="20" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="13">
-        <v>0.9</v>
-      </c>
-      <c r="D20" s="12">
+      <c r="C20" s="23">
         <v>1</v>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="H20" s="9" t="s">
+      <c r="D20" s="23">
+        <v>0.95</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="H20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="7" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="21" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B21" s="7" t="s">
+      <c r="K20" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="5">
         <v>1</v>
       </c>
-      <c r="D21" s="13">
-        <v>1.1</v>
-      </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="H21" s="9" t="s">
+      <c r="D21" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="H21" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="22" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B22" s="10" t="s">
+    <row r="22" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="9">
         <v>1</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="9">
         <v>1</v>
       </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="H22" s="9" t="s">
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="H22" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J22" s="10" t="s">
+      <c r="J22" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B23" s="7" t="s">
+    <row r="23" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="5">
         <v>1</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="5">
         <v>1</v>
       </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="H23" s="9" t="s">
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="H23" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J23" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B24" s="10" t="s">
+    <row r="24" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="9">
         <v>1</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="9">
         <v>1</v>
       </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
       <c r="G24" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="6" t="s">
         <v>47</v>
       </c>
       <c r="I24" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="J24" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B25" s="7" t="s">
+    <row r="25" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="23">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D25" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="H25" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="9">
         <v>1</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D26" s="9">
         <v>1</v>
       </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="H25" s="9" t="s">
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="H26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D27" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="H27" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="9">
+        <v>1</v>
+      </c>
+      <c r="D28" s="9">
+        <v>1</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="H28" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="5">
+        <v>1</v>
+      </c>
+      <c r="D29" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="H29" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="D30" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="H30" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="5">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="H31" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="9">
+        <v>1</v>
+      </c>
+      <c r="D32" s="9">
+        <v>1</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="H32" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="5">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="H33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="9">
+        <v>1</v>
+      </c>
+      <c r="D34" s="9">
+        <v>1</v>
+      </c>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="H34" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1</v>
+      </c>
+      <c r="D35" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="H35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D36" s="23">
+        <v>0.95</v>
+      </c>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="H36" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J25" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A26" s="6"/>
-      <c r="B26" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="12">
+      <c r="J36" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K36" s="22" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="5">
         <v>1</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D37" s="5">
         <v>1</v>
       </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="H26" s="9" t="s">
+      <c r="E37" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="H37" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="B38" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="9">
+        <v>1</v>
+      </c>
+      <c r="D38" s="9">
+        <v>1</v>
+      </c>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="H38" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J26" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B27" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D27" s="11">
+      <c r="J38" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="5">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5">
         <v>0.95</v>
       </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="H27" s="9" t="s">
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="H39" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+      <c r="B40" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="9">
+        <v>1</v>
+      </c>
+      <c r="D40" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="H40" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="D41" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="H41" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J27" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B28" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="12">
+    </row>
+    <row r="42" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="D42" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="H42" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="8">
         <v>1</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D43" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="H43" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="D44" s="9">
+        <v>0.85</v>
+      </c>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="H44" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="D45" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="H45" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D46" s="9">
+        <v>0.85</v>
+      </c>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="H46" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D47" s="10">
+        <v>0.85</v>
+      </c>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="H47" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" s="9">
         <v>1</v>
       </c>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="H28" s="9" t="s">
+      <c r="D48" s="9">
+        <v>0.85</v>
+      </c>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="H48" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J28" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B29" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="8">
-        <v>1</v>
-      </c>
-      <c r="D29" s="13">
-        <v>1.1</v>
-      </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="H29" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A30" s="6"/>
-      <c r="B30" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="13">
-        <v>0.95</v>
-      </c>
-      <c r="D30" s="13">
-        <v>1.1</v>
-      </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="H30" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B31" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="8">
-        <v>1</v>
-      </c>
-      <c r="D31" s="8">
-        <v>1</v>
-      </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="H31" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B32" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="12">
-        <v>1</v>
-      </c>
-      <c r="D32" s="12">
-        <v>1</v>
-      </c>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="H32" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="8">
-        <v>1</v>
-      </c>
-      <c r="D33" s="8">
-        <v>1</v>
-      </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="H33" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B34" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="12">
-        <v>1</v>
-      </c>
-      <c r="D34" s="12">
-        <v>1</v>
-      </c>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="H34" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B35" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="8">
-        <v>1</v>
-      </c>
-      <c r="D35" s="11">
-        <v>0.9</v>
-      </c>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="H35" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B36" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="11">
-        <v>1.1</v>
-      </c>
-      <c r="D36" s="12">
-        <v>1</v>
-      </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="H36" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B37" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="8">
-        <v>1</v>
-      </c>
-      <c r="D37" s="8">
-        <v>1</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="F37" s="8"/>
-      <c r="H37" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A38" s="6"/>
-      <c r="B38" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="12">
-        <v>1</v>
-      </c>
-      <c r="D38" s="12">
-        <v>1</v>
-      </c>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="H38" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="39" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B39" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C39" s="8">
-        <v>1</v>
-      </c>
-      <c r="D39" s="8">
-        <v>0.95</v>
-      </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="H39" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="40" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A40" s="6"/>
-      <c r="B40" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" s="12">
-        <v>1</v>
-      </c>
-      <c r="D40" s="12">
-        <v>1.1</v>
-      </c>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="H40" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J40" s="10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="41" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B41" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C41" s="8">
-        <v>1.05</v>
-      </c>
-      <c r="D41" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="H41" s="9" t="s">
+    </row>
+    <row r="49" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="D49" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="H49" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="42" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B42" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C42" s="11">
+    <row r="50" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D50" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="E50" s="12">
         <v>1.2</v>
       </c>
-      <c r="D42" s="11">
-        <v>0.85</v>
-      </c>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="H42" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B43" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C43" s="11">
-        <v>1</v>
-      </c>
-      <c r="D43" s="8">
-        <v>0.85</v>
-      </c>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="H43" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B44" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" s="12">
-        <v>1.05</v>
-      </c>
-      <c r="D44" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="H44" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B45" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" s="8">
-        <v>1.05</v>
-      </c>
-      <c r="D45" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="H45" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B46" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" s="13">
-        <v>1.15</v>
-      </c>
-      <c r="D46" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="H46" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B47" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C47" s="8">
-        <v>1.15</v>
-      </c>
-      <c r="D47" s="13">
-        <v>0.85</v>
-      </c>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="H47" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B48" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C48" s="12">
-        <v>1</v>
-      </c>
-      <c r="D48" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="H48" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B49" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="D49" s="11">
-        <v>0.7</v>
-      </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="H49" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B50" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" s="11">
-        <v>1.1</v>
-      </c>
-      <c r="D50" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="E50" s="15">
-        <v>1.2</v>
-      </c>
-      <c r="F50" s="15"/>
-      <c r="H50" s="9" t="s">
+      <c r="F50" s="12"/>
+      <c r="H50" s="6" t="s">
         <v>19</v>
       </c>
       <c r="I50" t="s">
         <v>28</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J50" s="11" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="51" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B51" s="7" t="s">
+    <row r="51" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C51" s="8">
         <v>1</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="5">
         <v>0.75</v>
       </c>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="H51" s="9" t="s">
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="H51" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="52" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B52" s="10" t="s">
+    <row r="52" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="12">
-        <v>1.1</v>
-      </c>
-      <c r="D52" s="12">
+      <c r="C52" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D52" s="9">
         <v>0.85</v>
       </c>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="H52" s="9" t="s">
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="H52" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="53" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B53" s="7" t="s">
+    <row r="53" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C53" s="8">
+      <c r="C53" s="5">
         <v>1.2</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="5">
         <v>0.85</v>
       </c>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="H53" s="9" t="s">
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="H53" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="54" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B54" s="7" t="s">
+    <row r="54" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C54" s="8">
-        <v>1.15</v>
-      </c>
-      <c r="D54" s="8">
+      <c r="C54" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D54" s="5">
         <v>0.8</v>
       </c>
-      <c r="E54" s="16">
+      <c r="E54" s="13">
         <v>1.2</v>
       </c>
-      <c r="F54" s="16"/>
-      <c r="H54" s="9" t="s">
+      <c r="F54" s="13"/>
+      <c r="H54" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="55" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B55" s="7" t="s">
+    <row r="55" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="8">
+      <c r="C55" s="5">
         <v>1</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="5">
         <v>0.85</v>
       </c>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="H55" s="9" t="s">
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="H55" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J55" s="19" t="s">
+      <c r="J55" s="25" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="56" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B56" s="10" t="s">
+    <row r="56" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="8">
+      <c r="C56" s="5">
         <v>1.05</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="5">
         <v>0.75</v>
       </c>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="H56" s="9" t="s">
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="H56" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="57" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B57" s="10" t="s">
+    <row r="57" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C57" s="8">
+      <c r="C57" s="5">
         <v>1.05</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="5">
         <v>1</v>
       </c>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="H57" s="9" t="s">
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="H57" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="58" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B58" s="7" t="s">
+    <row r="58" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="5">
         <v>1.05</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="5">
         <v>0.9</v>
       </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="H58" s="9" t="s">
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="H58" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="59" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B59" s="7" t="s">
+    <row r="59" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C59" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D59" s="8">
+      <c r="C59" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D59" s="5">
         <v>0.85</v>
       </c>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="H59" s="9" t="s">
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="H59" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J59" s="20"/>
-    </row>
-    <row r="60" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B60" s="7" t="s">
+      <c r="J59" s="26"/>
+    </row>
+    <row r="60" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C60" s="8">
+      <c r="C60" s="5">
         <v>1.2</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="5">
         <v>0.7</v>
       </c>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="H60" s="9" t="s">
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="H60" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="61" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B61" s="10" t="s">
+    <row r="61" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C61" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D61" s="8">
+      <c r="C61" s="23">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D61" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="H61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K61" s="22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C62" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D62" s="5">
         <v>0.8</v>
       </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="H61" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" ht="40.05" customHeight="1" spans="2:9">
-      <c r="B62" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C62" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D62" s="8">
-        <v>0.8</v>
-      </c>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
       <c r="G62" t="s">
         <v>32</v>
       </c>
-      <c r="H62" s="9" t="s">
+      <c r="H62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I62" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="63" ht="40.05" customHeight="1" spans="2:9">
-      <c r="B63" s="10" t="s">
+    <row r="63" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C63" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D63" s="8">
+      <c r="C63" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D63" s="5">
         <v>0.8</v>
       </c>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="H63" s="9" t="s">
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="H63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I63" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="64" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B64" s="10" t="s">
+    <row r="64" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C64" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D64" s="8">
+      <c r="C64" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D64" s="5">
         <v>0.95</v>
       </c>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="H64" s="9" t="s">
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="H64" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="65" ht="40.05" customHeight="1" spans="2:9">
-      <c r="B65" s="10" t="s">
+    <row r="65" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C65" s="8">
+      <c r="C65" s="5">
         <v>1.2</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="5">
         <v>0.9</v>
       </c>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
       <c r="G65" t="s">
         <v>120</v>
       </c>
-      <c r="H65" s="9" t="s">
+      <c r="H65" s="6" t="s">
         <v>44</v>
       </c>
       <c r="I65" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="66" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B66" s="7" t="s">
+    <row r="66" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C66" s="8">
+      <c r="C66" s="5">
         <v>1</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="5">
         <v>1.05</v>
       </c>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="H66" s="9" t="s">
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="H66" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="67" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B67" s="10" t="s">
+    <row r="67" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C67" s="8">
+      <c r="C67" s="5">
         <v>0.85</v>
       </c>
-      <c r="D67" s="8">
-        <v>1.15</v>
-      </c>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="H67" s="9" t="s">
+      <c r="D67" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="H67" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="68" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B68" s="7" t="s">
+    <row r="68" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C68" s="8">
+      <c r="C68" s="5">
         <v>0.8</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="5">
         <v>1.05</v>
       </c>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-      <c r="H68" s="9" t="s">
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="H68" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="69" ht="40.05" customHeight="1" spans="2:9">
-      <c r="B69" s="10" t="s">
+    <row r="69" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C69" s="8">
+      <c r="C69" s="5">
         <v>0.9</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="5">
         <v>1</v>
       </c>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
       <c r="G69" t="s">
         <v>126</v>
       </c>
-      <c r="H69" s="9" t="s">
+      <c r="H69" s="6" t="s">
         <v>44</v>
       </c>
       <c r="I69" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="70" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B70" s="7" t="s">
+    <row r="70" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C70" s="8">
+      <c r="C70" s="5">
         <v>1.05</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="5">
         <v>0.95</v>
       </c>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-      <c r="H70" s="9" t="s">
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="H70" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="71" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B71" s="10" t="s">
+    <row r="71" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C71" s="8">
+      <c r="C71" s="5">
         <v>1</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="5">
         <v>1</v>
       </c>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="H71" s="9" t="s">
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="H71" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="72" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B72" s="7" t="s">
+    <row r="72" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C72" s="8">
+      <c r="C72" s="5">
         <v>1</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="5">
         <v>1</v>
       </c>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
-      <c r="H72" s="9" t="s">
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
+      <c r="H72" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="73" ht="40.05" customHeight="1" spans="2:9">
-      <c r="B73" s="10" t="s">
+    <row r="73" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C73" s="8">
+      <c r="C73" s="5">
         <v>1.25</v>
       </c>
-      <c r="D73" s="8">
+      <c r="D73" s="5">
         <v>0.95</v>
       </c>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16"/>
-      <c r="H73" s="9" t="s">
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="H73" s="6" t="s">
         <v>44</v>
       </c>
       <c r="I73" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="74" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B74" s="7" t="s">
+    <row r="74" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C74" s="8">
+      <c r="C74" s="5">
         <v>1</v>
       </c>
-      <c r="D74" s="8">
+      <c r="D74" s="5">
         <v>1</v>
       </c>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="H74" s="9" t="s">
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="H74" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="75" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B75" s="10" t="s">
+    <row r="75" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C75" s="8">
+      <c r="C75" s="5">
         <v>0.9</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="5">
         <v>1</v>
       </c>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="H75" s="9" t="s">
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="H75" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="76" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B76" s="7" t="s">
+    <row r="76" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C76" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D76" s="8">
+      <c r="C76" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D76" s="5">
         <v>1</v>
       </c>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="H76" s="9" t="s">
+      <c r="E76" s="13"/>
+      <c r="F76" s="13"/>
+      <c r="H76" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="77" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B77" s="10" t="s">
+    <row r="77" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C77" s="8">
+      <c r="C77" s="5">
         <v>0.9</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="5">
         <v>1</v>
       </c>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="H77" s="9" t="s">
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="H77" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="78" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B78" s="7" t="s">
+    <row r="78" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C78" s="8">
+      <c r="C78" s="5">
         <v>1</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="5">
         <v>0.95</v>
       </c>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="H78" s="9" t="s">
+      <c r="E78" s="13"/>
+      <c r="F78" s="13"/>
+      <c r="H78" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="79" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B79" s="10" t="s">
+    <row r="79" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C79" s="8">
+      <c r="C79" s="5">
         <v>1.05</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="5">
         <v>0.85</v>
       </c>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="H79" s="9" t="s">
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="H79" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="80" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B80" s="7" t="s">
+    <row r="80" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C80" s="8">
+      <c r="C80" s="5">
         <v>1</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="5">
         <v>1</v>
       </c>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="H80" s="9" t="s">
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
+      <c r="H80" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="81" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B81" s="10" t="s">
+    <row r="81" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C81" s="8">
+      <c r="C81" s="5">
         <v>1.05</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D81" s="5">
         <v>0.9</v>
       </c>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16"/>
-      <c r="H81" s="9" t="s">
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="H81" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="82" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B82" s="7" t="s">
+    <row r="82" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C82" s="8">
+      <c r="C82" s="5">
         <v>0.9</v>
       </c>
-      <c r="D82" s="8">
+      <c r="D82" s="5">
         <v>1.05</v>
       </c>
-      <c r="E82" s="16"/>
-      <c r="F82" s="16"/>
-      <c r="H82" s="9" t="s">
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="H82" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="83" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B83" s="10" t="s">
+    <row r="83" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C83" s="8">
+      <c r="C83" s="5">
         <v>0.9</v>
       </c>
-      <c r="D83" s="8">
+      <c r="D83" s="5">
         <v>1.05</v>
       </c>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16"/>
-      <c r="H83" s="9" t="s">
+      <c r="E83" s="13"/>
+      <c r="F83" s="13"/>
+      <c r="H83" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="84" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B84" s="7" t="s">
+    <row r="84" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C84" s="8">
+      <c r="C84" s="5">
         <v>1.05</v>
       </c>
-      <c r="D84" s="8">
+      <c r="D84" s="5">
         <v>0.95</v>
       </c>
-      <c r="E84" s="16"/>
-      <c r="F84" s="16"/>
-      <c r="H84" s="9" t="s">
+      <c r="E84" s="13"/>
+      <c r="F84" s="13"/>
+      <c r="H84" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="85" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B85" s="10" t="s">
+    <row r="85" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C85" s="8">
+      <c r="C85" s="5">
         <v>1</v>
       </c>
-      <c r="D85" s="8">
+      <c r="D85" s="5">
         <v>1</v>
       </c>
-      <c r="E85" s="16"/>
-      <c r="F85" s="16"/>
-      <c r="H85" s="9" t="s">
+      <c r="E85" s="13"/>
+      <c r="F85" s="13"/>
+      <c r="H85" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="86" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B86" s="10" t="s">
+    <row r="86" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C86" s="8">
-        <v>1.15</v>
-      </c>
-      <c r="D86" s="8">
+      <c r="C86" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D86" s="5">
         <v>0.8</v>
       </c>
-      <c r="E86" s="16"/>
-      <c r="F86" s="16"/>
-      <c r="H86" s="9" t="s">
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="H86" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="87" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B87" s="7" t="s">
+    <row r="87" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="8">
+      <c r="C87" s="5">
         <v>0.9</v>
       </c>
-      <c r="D87" s="8">
+      <c r="D87" s="5">
         <v>1.05</v>
       </c>
-      <c r="E87" s="16"/>
-      <c r="F87" s="16"/>
-      <c r="H87" s="9" t="s">
+      <c r="E87" s="13"/>
+      <c r="F87" s="13"/>
+      <c r="H87" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="88" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B88" s="10" t="s">
+    <row r="88" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C88" s="8">
+      <c r="C88" s="5">
         <v>0.9</v>
       </c>
-      <c r="D88" s="8">
+      <c r="D88" s="5">
         <v>1.05</v>
       </c>
-      <c r="E88" s="16"/>
-      <c r="F88" s="16"/>
-      <c r="H88" s="9" t="s">
+      <c r="E88" s="13"/>
+      <c r="F88" s="13"/>
+      <c r="H88" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="89" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B89" s="7" t="s">
+    <row r="89" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C89" s="8">
+      <c r="C89" s="5">
         <v>1.05</v>
       </c>
-      <c r="D89" s="8">
+      <c r="D89" s="5">
         <v>0.95</v>
       </c>
-      <c r="E89" s="16"/>
-      <c r="F89" s="16"/>
-      <c r="H89" s="9" t="s">
+      <c r="E89" s="13"/>
+      <c r="F89" s="13"/>
+      <c r="H89" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="90" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B90" s="10" t="s">
+    <row r="90" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C90" s="8">
+      <c r="C90" s="5">
         <v>1</v>
       </c>
-      <c r="D90" s="8">
+      <c r="D90" s="5">
         <v>0.9</v>
       </c>
-      <c r="E90" s="16"/>
-      <c r="F90" s="16"/>
-      <c r="H90" s="9" t="s">
+      <c r="E90" s="13"/>
+      <c r="F90" s="13"/>
+      <c r="H90" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="91" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B91" s="7" t="s">
+    <row r="91" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C91" s="8">
+      <c r="C91" s="5">
         <v>1</v>
       </c>
-      <c r="D91" s="8">
+      <c r="D91" s="5">
         <v>1</v>
       </c>
-      <c r="E91" s="16">
+      <c r="E91" s="13">
         <v>0.9</v>
       </c>
-      <c r="F91" s="16"/>
-      <c r="H91" s="9" t="s">
+      <c r="F91" s="13"/>
+      <c r="H91" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="92" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B92" s="10" t="s">
+    <row r="92" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C92" s="8">
+      <c r="C92" s="5">
         <v>0.95</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="5">
         <v>1</v>
       </c>
-      <c r="E92" s="16"/>
-      <c r="F92" s="16"/>
-      <c r="H92" s="9" t="s">
+      <c r="E92" s="13"/>
+      <c r="F92" s="13"/>
+      <c r="H92" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="93" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B93" s="7" t="s">
+    <row r="93" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C93" s="8">
+      <c r="C93" s="5">
         <v>0.95</v>
       </c>
-      <c r="D93" s="8">
+      <c r="D93" s="5">
         <v>1.05</v>
       </c>
-      <c r="E93" s="16"/>
-      <c r="F93" s="16"/>
-      <c r="H93" s="9" t="s">
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
+      <c r="H93" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="94" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B94" s="10" t="s">
+    <row r="94" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C94" s="8">
+      <c r="C94" s="5">
         <v>1</v>
       </c>
-      <c r="D94" s="8">
+      <c r="D94" s="5">
         <v>0.9</v>
       </c>
-      <c r="E94" s="16"/>
-      <c r="F94" s="16"/>
-      <c r="H94" s="9" t="s">
+      <c r="E94" s="13"/>
+      <c r="F94" s="13"/>
+      <c r="H94" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="95" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B95" s="7" t="s">
+    <row r="95" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C95" s="8">
+      <c r="C95" s="5">
         <v>1.05</v>
       </c>
-      <c r="D95" s="8">
+      <c r="D95" s="5">
         <v>0.95</v>
       </c>
-      <c r="E95" s="16"/>
-      <c r="F95" s="16"/>
-      <c r="H95" s="9" t="s">
+      <c r="E95" s="13"/>
+      <c r="F95" s="13"/>
+      <c r="H95" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="96" ht="40.05" customHeight="1" spans="2:9">
-      <c r="B96" s="10" t="s">
+    <row r="96" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C96" s="8">
+      <c r="C96" s="5">
         <v>1</v>
       </c>
-      <c r="D96" s="8">
+      <c r="D96" s="5">
         <v>0.85</v>
       </c>
-      <c r="E96" s="16"/>
-      <c r="F96" s="16"/>
-      <c r="H96" s="9" t="s">
+      <c r="E96" s="13"/>
+      <c r="F96" s="13"/>
+      <c r="H96" s="6" t="s">
         <v>47</v>
       </c>
       <c r="I96" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="97" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B97" s="10" t="s">
+    <row r="97" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C97" s="8">
+      <c r="C97" s="5">
         <v>1</v>
       </c>
-      <c r="D97" s="8">
+      <c r="D97" s="5">
         <v>0.95</v>
       </c>
-      <c r="E97" s="16"/>
-      <c r="F97" s="16"/>
-      <c r="H97" s="9" t="s">
+      <c r="E97" s="13"/>
+      <c r="F97" s="13"/>
+      <c r="H97" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="98" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B98" s="7" t="s">
+    <row r="98" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C98" s="8">
+      <c r="C98" s="5">
         <v>1</v>
       </c>
-      <c r="D98" s="8">
+      <c r="D98" s="5">
         <v>1</v>
       </c>
-      <c r="E98" s="16"/>
-      <c r="F98" s="16"/>
-      <c r="H98" s="9" t="s">
+      <c r="E98" s="13"/>
+      <c r="F98" s="13"/>
+      <c r="H98" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="99" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B99" s="10" t="s">
+    <row r="99" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C99" s="8">
+      <c r="C99" s="5">
         <v>1</v>
       </c>
-      <c r="D99" s="8">
-        <v>1.15</v>
-      </c>
-      <c r="E99" s="16">
+      <c r="D99" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E99" s="13">
         <v>0.85</v>
       </c>
-      <c r="F99" s="16">
+      <c r="F99" s="13">
         <v>0.85</v>
       </c>
-      <c r="H99" s="9" t="s">
+      <c r="H99" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="100" ht="40.05" customHeight="1" spans="2:9">
-      <c r="B100" s="7" t="s">
+    <row r="100" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C100" s="8">
+      <c r="C100" s="5">
         <v>0.95</v>
       </c>
-      <c r="D100" s="8">
+      <c r="D100" s="5">
         <v>1.05</v>
       </c>
-      <c r="E100" s="16"/>
-      <c r="F100" s="16"/>
+      <c r="E100" s="13"/>
+      <c r="F100" s="13"/>
       <c r="G100" t="s">
         <v>160</v>
       </c>
-      <c r="H100" s="9" t="s">
+      <c r="H100" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I100" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="101" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B101" s="10" t="s">
+    <row r="101" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C101" s="8">
+      <c r="C101" s="5">
         <v>1</v>
       </c>
-      <c r="D101" s="8">
+      <c r="D101" s="5">
         <v>1</v>
       </c>
-      <c r="E101" s="16"/>
-      <c r="F101" s="16"/>
-      <c r="H101" s="9" t="s">
+      <c r="E101" s="13"/>
+      <c r="F101" s="13"/>
+      <c r="H101" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J101" t="s">
+      <c r="J101" s="11" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="102" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B102" s="7" t="s">
+    <row r="102" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C102" s="8">
+      <c r="C102" s="5">
         <v>1</v>
       </c>
-      <c r="D102" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="E102" s="16">
+      <c r="D102" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E102" s="13">
         <v>0.9</v>
       </c>
-      <c r="F102" s="16"/>
-      <c r="H102" s="9" t="s">
+      <c r="F102" s="13"/>
+      <c r="H102" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="103" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B103" s="10" t="s">
+    <row r="103" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C103" s="8">
+      <c r="C103" s="5">
         <v>1</v>
       </c>
-      <c r="D103" s="8">
-        <v>1</v>
-      </c>
-      <c r="E103" s="16"/>
-      <c r="F103" s="16"/>
-      <c r="H103" s="9" t="s">
+      <c r="D103" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="E103" s="13"/>
+      <c r="F103" s="13"/>
+      <c r="H103" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="104" ht="40.05" customHeight="1" spans="2:9">
-      <c r="B104" s="7" t="s">
+      <c r="K103" s="22" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C104" s="8">
-        <v>1.15</v>
-      </c>
-      <c r="D104" s="8">
+      <c r="C104" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D104" s="5">
         <v>0.85</v>
       </c>
-      <c r="E104" s="16"/>
-      <c r="F104" s="16"/>
+      <c r="E104" s="13"/>
+      <c r="F104" s="13"/>
       <c r="G104" t="s">
         <v>166</v>
       </c>
-      <c r="H104" s="9" t="s">
+      <c r="H104" s="6" t="s">
         <v>47</v>
       </c>
       <c r="I104" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="105" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B105" s="10" t="s">
+    <row r="105" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C105" s="8">
+      <c r="C105" s="5">
         <v>0.8</v>
       </c>
-      <c r="D105" s="8">
+      <c r="D105" s="5">
         <v>1.2</v>
       </c>
-      <c r="E105" s="16">
+      <c r="E105" s="13">
         <v>0.75</v>
       </c>
-      <c r="F105" s="16">
+      <c r="F105" s="13">
         <v>0.75</v>
       </c>
-      <c r="H105" s="9" t="s">
+      <c r="H105" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="106" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B106" s="7" t="s">
+    <row r="106" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C106" s="8">
+      <c r="C106" s="5">
         <v>1</v>
       </c>
-      <c r="D106" s="8">
+      <c r="D106" s="5">
         <v>1.05</v>
       </c>
-      <c r="E106" s="16">
+      <c r="E106" s="13">
         <v>0.75</v>
       </c>
-      <c r="F106" s="16">
+      <c r="F106" s="13">
         <v>0.75</v>
       </c>
-      <c r="H106" s="9" t="s">
+      <c r="H106" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="107" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B107" s="10" t="s">
+    <row r="107" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C107" s="8">
+      <c r="C107" s="5">
         <v>1</v>
       </c>
-      <c r="D107" s="8">
+      <c r="D107" s="5">
         <v>0.75</v>
       </c>
-      <c r="E107" s="16"/>
-      <c r="F107" s="16"/>
-      <c r="H107" s="9" t="s">
+      <c r="E107" s="13"/>
+      <c r="F107" s="13"/>
+      <c r="H107" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="108" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B108" s="7" t="s">
+    <row r="108" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C108" s="8">
+      <c r="C108" s="5">
         <v>1</v>
       </c>
-      <c r="D108" s="8">
+      <c r="D108" s="5">
         <v>1</v>
       </c>
-      <c r="E108" s="16"/>
-      <c r="F108" s="16"/>
-      <c r="H108" s="9" t="s">
+      <c r="E108" s="13"/>
+      <c r="F108" s="13"/>
+      <c r="H108" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="109" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B109" s="10" t="s">
+    <row r="109" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="C109" s="8">
+      <c r="C109" s="5">
         <v>1</v>
       </c>
-      <c r="D109" s="8">
+      <c r="D109" s="5">
         <v>0.95</v>
       </c>
-      <c r="E109" s="16">
+      <c r="E109" s="13">
         <v>0.8</v>
       </c>
-      <c r="F109" s="16">
+      <c r="F109" s="13">
         <v>0.8</v>
       </c>
-      <c r="H109" s="9" t="s">
+      <c r="H109" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J109" t="s">
+      <c r="J109" s="11" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="110" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B110" s="7" t="s">
+    <row r="110" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C110" s="8">
+      <c r="C110" s="5">
         <v>0.85</v>
       </c>
-      <c r="D110" s="8">
+      <c r="D110" s="5">
         <v>1</v>
       </c>
-      <c r="E110" s="16"/>
-      <c r="F110" s="16"/>
-      <c r="H110" s="9" t="s">
+      <c r="E110" s="13"/>
+      <c r="F110" s="13"/>
+      <c r="H110" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="111" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B111" s="10" t="s">
+    <row r="111" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="C111" s="8">
+      <c r="C111" s="5">
         <v>1</v>
       </c>
-      <c r="D111" s="8">
+      <c r="D111" s="5">
         <v>1</v>
       </c>
-      <c r="E111" s="16"/>
-      <c r="F111" s="16"/>
-      <c r="H111" s="9" t="s">
+      <c r="E111" s="13"/>
+      <c r="F111" s="13"/>
+      <c r="H111" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="112" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B112" s="7" t="s">
+    <row r="112" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B112" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C112" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D112" s="8">
+      <c r="C112" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D112" s="5">
         <v>0.9</v>
       </c>
-      <c r="E112" s="16"/>
-      <c r="F112" s="16"/>
-      <c r="H112" s="9" t="s">
+      <c r="E112" s="13"/>
+      <c r="F112" s="13"/>
+      <c r="H112" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="113" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B113" s="10" t="s">
+    <row r="113" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C113" s="8">
+      <c r="C113" s="5">
         <v>1.05</v>
       </c>
-      <c r="D113" s="8">
+      <c r="D113" s="5">
         <v>0.7</v>
       </c>
-      <c r="E113" s="8"/>
-      <c r="F113" s="8"/>
-      <c r="H113" s="9" t="s">
+      <c r="E113" s="5"/>
+      <c r="F113" s="5"/>
+      <c r="H113" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="114" ht="40.05" customHeight="1" spans="1:8">
-      <c r="A114" s="21"/>
-      <c r="B114" s="7" t="s">
+    <row r="114" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="16"/>
+      <c r="B114" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C114" s="8">
+      <c r="C114" s="5">
         <v>0.9</v>
       </c>
-      <c r="D114" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="E114" s="8"/>
-      <c r="F114" s="8"/>
-      <c r="H114" s="9" t="s">
+      <c r="D114" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E114" s="5"/>
+      <c r="F114" s="5"/>
+      <c r="H114" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="115" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B115" s="7" t="s">
+    <row r="115" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C115" s="8">
+      <c r="C115" s="5">
         <v>0.9</v>
       </c>
-      <c r="D115" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
-      <c r="H115" s="9" t="s">
+      <c r="D115" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E115" s="5"/>
+      <c r="F115" s="5"/>
+      <c r="H115" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J115" s="22" t="s">
+      <c r="J115" s="27" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="116" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B116" s="7" t="s">
+    <row r="116" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B116" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C116" s="8">
+      <c r="C116" s="5">
         <v>0.95</v>
       </c>
-      <c r="D116" s="8">
+      <c r="D116" s="5">
         <v>0.85</v>
       </c>
-      <c r="E116" s="8"/>
-      <c r="F116" s="8"/>
-      <c r="H116" s="9" t="s">
+      <c r="E116" s="5"/>
+      <c r="F116" s="5"/>
+      <c r="H116" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="117" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B117" s="7" t="s">
+    <row r="117" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C117" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D117" s="8">
+      <c r="C117" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D117" s="5">
         <v>0.9</v>
       </c>
-      <c r="E117" s="8"/>
-      <c r="F117" s="8"/>
-      <c r="H117" s="9" t="s">
+      <c r="E117" s="5"/>
+      <c r="F117" s="5"/>
+      <c r="H117" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="118" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B118" s="7" t="s">
+    <row r="118" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C118" s="8">
+      <c r="C118" s="5">
         <v>1.05</v>
       </c>
-      <c r="D118" s="8">
+      <c r="D118" s="5">
         <v>0.75</v>
       </c>
-      <c r="E118" s="8"/>
-      <c r="F118" s="8"/>
-      <c r="H118" s="9" t="s">
+      <c r="E118" s="5"/>
+      <c r="F118" s="5"/>
+      <c r="H118" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="119" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B119" s="7" t="s">
+    <row r="119" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B119" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C119" s="8">
+      <c r="C119" s="5">
         <v>1</v>
       </c>
-      <c r="D119" s="8">
+      <c r="D119" s="5">
         <v>1</v>
       </c>
-      <c r="E119" s="8"/>
-      <c r="F119" s="8"/>
-      <c r="H119" s="9" t="s">
+      <c r="E119" s="5"/>
+      <c r="F119" s="5"/>
+      <c r="H119" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="120" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B120" s="7" t="s">
+    <row r="120" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C120" s="8">
+      <c r="C120" s="5">
         <v>1.05</v>
       </c>
-      <c r="D120" s="8">
+      <c r="D120" s="5">
         <v>0.85</v>
       </c>
-      <c r="E120" s="8"/>
-      <c r="F120" s="8"/>
-      <c r="H120" s="9" t="s">
+      <c r="E120" s="5"/>
+      <c r="F120" s="5"/>
+      <c r="H120" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J120" t="s">
+      <c r="J120" s="11" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="121" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B121" s="7" t="s">
+    <row r="121" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C121" s="8">
+      <c r="C121" s="5">
         <v>1</v>
       </c>
-      <c r="D121" s="8">
+      <c r="D121" s="5">
         <v>0.9</v>
       </c>
-      <c r="E121" s="8"/>
-      <c r="F121" s="8"/>
-      <c r="H121" s="9" t="s">
+      <c r="E121" s="5"/>
+      <c r="F121" s="5"/>
+      <c r="H121" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="122" ht="40.05" customHeight="1" spans="2:8">
-      <c r="B122" s="7" t="s">
+    <row r="122" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C122" s="8">
+      <c r="C122" s="5">
         <v>1</v>
       </c>
-      <c r="D122" s="8">
+      <c r="D122" s="5">
         <v>0.95</v>
       </c>
-      <c r="E122" s="8"/>
-      <c r="F122" s="8"/>
-      <c r="H122" s="9" t="s">
+      <c r="E122" s="5"/>
+      <c r="F122" s="5"/>
+      <c r="H122" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="123" ht="40.05" customHeight="1" spans="1:8">
-      <c r="A123" s="21"/>
-      <c r="B123" s="7" t="s">
+    <row r="123" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="16"/>
+      <c r="B123" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C123" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D123" s="8">
+      <c r="C123" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D123" s="5">
         <v>1</v>
       </c>
-      <c r="E123" s="8"/>
-      <c r="F123" s="8"/>
-      <c r="H123" s="9" t="s">
+      <c r="E123" s="5"/>
+      <c r="F123" s="5"/>
+      <c r="H123" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="124" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B124" s="7" t="s">
+    <row r="124" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C124" s="8">
+      <c r="C124" s="5">
         <v>1.05</v>
       </c>
-      <c r="D124" s="8">
+      <c r="D124" s="5">
         <v>0.95</v>
       </c>
-      <c r="E124" s="8"/>
-      <c r="F124" s="8"/>
-      <c r="H124" s="9" t="s">
+      <c r="E124" s="5"/>
+      <c r="F124" s="5"/>
+      <c r="H124" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J124" s="7"/>
-    </row>
-    <row r="125" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A125" s="21"/>
-      <c r="B125" s="7" t="s">
+      <c r="J124" s="4"/>
+    </row>
+    <row r="125" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="16"/>
+      <c r="B125" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C125" s="8">
+      <c r="C125" s="5">
         <v>1.05</v>
       </c>
-      <c r="D125" s="8">
+      <c r="D125" s="5">
         <v>0.85</v>
       </c>
-      <c r="E125" s="8"/>
-      <c r="F125" s="8"/>
-      <c r="H125" s="9" t="s">
+      <c r="E125" s="5"/>
+      <c r="F125" s="5"/>
+      <c r="H125" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J125" s="7"/>
-    </row>
-    <row r="126" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B126" s="7" t="s">
+      <c r="J125" s="4"/>
+    </row>
+    <row r="126" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C126" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D126" s="8">
+      <c r="C126" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D126" s="5">
         <v>0.9</v>
       </c>
-      <c r="E126" s="8"/>
-      <c r="F126" s="8"/>
-      <c r="H126" s="9" t="s">
+      <c r="E126" s="5"/>
+      <c r="F126" s="5"/>
+      <c r="H126" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J126" s="7"/>
-    </row>
-    <row r="127" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B127" s="7" t="s">
+      <c r="J126" s="4"/>
+    </row>
+    <row r="127" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C127" s="8">
+      <c r="C127" s="5">
         <v>1</v>
       </c>
-      <c r="D127" s="8">
+      <c r="D127" s="5">
         <v>1</v>
       </c>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
-      <c r="H127" s="9" t="s">
+      <c r="E127" s="5"/>
+      <c r="F127" s="5"/>
+      <c r="H127" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="J127" s="7"/>
-    </row>
-    <row r="128" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B128" s="7" t="s">
+      <c r="J127" s="4"/>
+    </row>
+    <row r="128" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B128" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C128" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D128" s="8">
+      <c r="C128" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D128" s="5">
         <v>0.9</v>
       </c>
-      <c r="E128" s="8"/>
-      <c r="F128" s="8"/>
+      <c r="E128" s="5"/>
+      <c r="F128" s="5"/>
       <c r="G128" t="s">
         <v>194</v>
       </c>
-      <c r="H128" s="9" t="s">
+      <c r="H128" s="6" t="s">
         <v>47</v>
       </c>
       <c r="I128" t="s">
         <v>121</v>
       </c>
-      <c r="J128" s="7"/>
-    </row>
-    <row r="129" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B129" s="7" t="s">
+      <c r="J128" s="4"/>
+    </row>
+    <row r="129" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B129" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C129" s="8">
+      <c r="C129" s="5">
         <v>0.95</v>
       </c>
-      <c r="D129" s="8">
+      <c r="D129" s="5">
         <v>1.05</v>
       </c>
-      <c r="E129" s="8"/>
-      <c r="F129" s="8"/>
-      <c r="H129" s="9" t="s">
+      <c r="E129" s="5"/>
+      <c r="F129" s="5"/>
+      <c r="H129" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="J129" s="7"/>
-    </row>
-    <row r="130" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A130" s="21"/>
-      <c r="B130" s="7" t="s">
+      <c r="J129" s="4"/>
+    </row>
+    <row r="130" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="16"/>
+      <c r="B130" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C130" s="8">
+      <c r="C130" s="5">
         <v>1.05</v>
       </c>
-      <c r="D130" s="8">
+      <c r="D130" s="5">
         <v>0.8</v>
       </c>
-      <c r="E130" s="8"/>
-      <c r="F130" s="8"/>
+      <c r="E130" s="5"/>
+      <c r="F130" s="5"/>
       <c r="G130" t="s">
         <v>197</v>
       </c>
-      <c r="H130" s="9" t="s">
+      <c r="H130" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I130" t="s">
         <v>198</v>
       </c>
-      <c r="J130" s="7"/>
-    </row>
-    <row r="131" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B131" s="7" t="s">
+      <c r="J130" s="4"/>
+    </row>
+    <row r="131" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C131" s="8">
+      <c r="C131" s="5">
         <v>1</v>
       </c>
-      <c r="D131" s="8">
+      <c r="D131" s="5">
         <v>1</v>
       </c>
-      <c r="E131" s="8"/>
-      <c r="F131" s="8"/>
-      <c r="H131" s="9" t="s">
+      <c r="E131" s="5"/>
+      <c r="F131" s="5"/>
+      <c r="H131" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J131" s="7"/>
-    </row>
-    <row r="132" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B132" s="7" t="s">
+      <c r="J131" s="4"/>
+    </row>
+    <row r="132" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B132" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C132" s="8">
+      <c r="C132" s="5">
         <v>1.05</v>
       </c>
-      <c r="D132" s="8">
+      <c r="D132" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="E132" s="5"/>
+      <c r="F132" s="5"/>
+      <c r="H132" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J132" s="4"/>
+      <c r="K132" s="22" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C133" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D133" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="E133" s="5"/>
+      <c r="F133" s="5"/>
+      <c r="H133" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J133" s="4"/>
+      <c r="K133" s="22" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B134" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C134" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="D134" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="E134" s="5"/>
+      <c r="F134" s="5"/>
+      <c r="H134" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J134" s="4"/>
+    </row>
+    <row r="135" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B135" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C135" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D135" s="5">
         <v>0.9</v>
       </c>
-      <c r="E132" s="8"/>
-      <c r="F132" s="8"/>
-      <c r="H132" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J132" s="7"/>
-    </row>
-    <row r="133" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B133" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C133" s="8">
-        <v>1.05</v>
-      </c>
-      <c r="D133" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
-      <c r="H133" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J133" s="7"/>
-    </row>
-    <row r="134" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B134" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C134" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="D134" s="8">
-        <v>0.8</v>
-      </c>
-      <c r="E134" s="8"/>
-      <c r="F134" s="8"/>
-      <c r="H134" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="J134" s="7"/>
-    </row>
-    <row r="135" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B135" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C135" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D135" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="E135" s="8"/>
-      <c r="F135" s="8"/>
+      <c r="E135" s="5"/>
+      <c r="F135" s="5"/>
       <c r="G135" t="s">
         <v>204</v>
       </c>
-      <c r="H135" s="9" t="s">
+      <c r="H135" s="6" t="s">
         <v>19</v>
       </c>
       <c r="I135" t="s">
         <v>205</v>
       </c>
-      <c r="J135" s="7"/>
-    </row>
-    <row r="136" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A136" s="21"/>
-      <c r="B136" s="7" t="s">
+      <c r="J135" s="4"/>
+    </row>
+    <row r="136" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="16"/>
+      <c r="B136" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C136" s="8">
+      <c r="C136" s="5">
         <v>1</v>
       </c>
-      <c r="D136" s="8">
+      <c r="D136" s="5">
         <v>1</v>
       </c>
-      <c r="E136" s="8"/>
-      <c r="F136" s="8"/>
-      <c r="H136" s="9" t="s">
+      <c r="E136" s="5"/>
+      <c r="F136" s="5"/>
+      <c r="H136" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J136" s="7"/>
-    </row>
-    <row r="137" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B137" s="7" t="s">
+      <c r="J136" s="4"/>
+    </row>
+    <row r="137" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B137" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C137" s="8">
+      <c r="C137" s="5">
         <v>1</v>
       </c>
-      <c r="D137" s="8">
+      <c r="D137" s="5">
         <v>0.9</v>
       </c>
-      <c r="E137" s="8"/>
-      <c r="F137" s="8"/>
-      <c r="H137" s="9" t="s">
+      <c r="E137" s="5"/>
+      <c r="F137" s="5"/>
+      <c r="H137" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J137" s="7"/>
-    </row>
-    <row r="138" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B138" s="7" t="s">
+      <c r="J137" s="4"/>
+    </row>
+    <row r="138" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B138" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C138" s="8">
+      <c r="C138" s="5">
         <v>1.05</v>
       </c>
-      <c r="D138" s="8">
+      <c r="D138" s="5">
         <v>0.8</v>
       </c>
-      <c r="E138" s="8"/>
-      <c r="F138" s="8"/>
-      <c r="H138" s="23" t="s">
+      <c r="E138" s="5"/>
+      <c r="F138" s="5"/>
+      <c r="H138" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J138" s="7"/>
-    </row>
-    <row r="139" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B139" s="7" t="s">
+      <c r="J138" s="4"/>
+    </row>
+    <row r="139" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B139" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C139" s="8">
+      <c r="C139" s="5">
         <v>0.8</v>
       </c>
-      <c r="D139" s="8">
+      <c r="D139" s="5">
         <v>1.2</v>
       </c>
-      <c r="E139" s="8">
+      <c r="E139" s="5">
         <v>0.8</v>
       </c>
-      <c r="F139" s="8">
+      <c r="F139" s="5">
         <v>0.8</v>
       </c>
-      <c r="H139" s="9" t="s">
+      <c r="H139" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J139" s="7"/>
-    </row>
-    <row r="140" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B140" s="7" t="s">
+      <c r="J139" s="4"/>
+    </row>
+    <row r="140" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B140" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C140" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D140" s="8">
+      <c r="C140" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D140" s="5">
         <v>0.8</v>
       </c>
-      <c r="E140" s="8"/>
-      <c r="F140" s="8"/>
-      <c r="H140" s="9" t="s">
+      <c r="E140" s="5"/>
+      <c r="F140" s="5"/>
+      <c r="H140" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J140" s="7"/>
-    </row>
-    <row r="141" ht="40.05" customHeight="1" spans="1:10">
-      <c r="A141" s="21"/>
-      <c r="B141" s="7" t="s">
+      <c r="J140" s="4"/>
+    </row>
+    <row r="141" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="16"/>
+      <c r="B141" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C141" s="8">
+      <c r="C141" s="5">
         <v>0.9</v>
       </c>
-      <c r="D141" s="8">
+      <c r="D141" s="5">
         <v>1</v>
       </c>
-      <c r="E141" s="8"/>
-      <c r="F141" s="8"/>
-      <c r="H141" s="9" t="s">
+      <c r="E141" s="5"/>
+      <c r="F141" s="5"/>
+      <c r="H141" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J141" s="7"/>
-    </row>
-    <row r="142" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B142" s="7" t="s">
+      <c r="J141" s="4"/>
+    </row>
+    <row r="142" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B142" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C142" s="8">
+      <c r="C142" s="5">
         <v>1</v>
       </c>
-      <c r="D142" s="8">
+      <c r="D142" s="5">
         <v>1.05</v>
       </c>
-      <c r="E142" s="8"/>
-      <c r="F142" s="8"/>
-      <c r="H142" s="9" t="s">
+      <c r="E142" s="5"/>
+      <c r="F142" s="5"/>
+      <c r="H142" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J142" s="7"/>
-    </row>
-    <row r="143" ht="40.05" customHeight="1" spans="2:10">
-      <c r="B143" s="7" t="s">
+      <c r="J142" s="4"/>
+    </row>
+    <row r="143" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B143" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C143" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D143" s="8">
+      <c r="C143" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D143" s="5">
         <v>0.7</v>
       </c>
-      <c r="E143" s="8"/>
-      <c r="F143" s="8"/>
+      <c r="E143" s="5"/>
+      <c r="F143" s="5"/>
       <c r="G143" t="s">
         <v>32</v>
       </c>
-      <c r="H143" s="9" t="s">
+      <c r="H143" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I143" t="s">
         <v>33</v>
       </c>
-      <c r="J143" s="7"/>
-    </row>
-    <row r="144" ht="15" customHeight="1" spans="10:10">
-      <c r="J144" s="7"/>
-    </row>
-    <row r="145" ht="15" customHeight="1" spans="10:10">
-      <c r="J145" s="7"/>
-    </row>
-    <row r="146" ht="15" customHeight="1" spans="10:10">
-      <c r="J146" s="7"/>
-    </row>
-    <row r="147" ht="15" customHeight="1" spans="10:10">
-      <c r="J147" s="7"/>
-    </row>
-    <row r="148" ht="15" customHeight="1" spans="10:10">
-      <c r="J148" s="7"/>
-    </row>
-    <row r="149" ht="15" customHeight="1" spans="10:10">
-      <c r="J149" s="7"/>
-    </row>
-    <row r="150" ht="15" customHeight="1" spans="10:10">
-      <c r="J150" s="7"/>
-    </row>
-    <row r="151" ht="15" customHeight="1" spans="10:10">
-      <c r="J151" s="7"/>
-    </row>
-    <row r="152" ht="15" customHeight="1" spans="10:10">
-      <c r="J152" s="7"/>
-    </row>
-    <row r="153" ht="15" customHeight="1" spans="10:10">
-      <c r="J153" s="7"/>
-    </row>
-    <row r="154" ht="15" customHeight="1" spans="10:10">
-      <c r="J154" s="7"/>
-    </row>
-    <row r="155" ht="15" customHeight="1" spans="10:10">
-      <c r="J155" s="7"/>
-    </row>
-    <row r="156" ht="15" customHeight="1" spans="10:10">
-      <c r="J156" s="7"/>
-    </row>
-    <row r="157" ht="15" customHeight="1" spans="10:10">
-      <c r="J157" s="7"/>
-    </row>
-    <row r="158" ht="15" customHeight="1" spans="10:10">
-      <c r="J158" s="7"/>
-    </row>
-    <row r="159" ht="15" customHeight="1" spans="10:10">
-      <c r="J159" s="7"/>
-    </row>
-    <row r="160" ht="15" customHeight="1" spans="10:10">
-      <c r="J160" s="7"/>
-    </row>
-    <row r="161" ht="15" customHeight="1" spans="10:10">
-      <c r="J161" s="7"/>
-    </row>
-    <row r="162" ht="15" customHeight="1" spans="10:10">
-      <c r="J162" s="7"/>
-    </row>
-    <row r="163" ht="15" customHeight="1" spans="10:10">
-      <c r="J163" s="7"/>
-    </row>
-    <row r="164" ht="15" customHeight="1" spans="10:10">
-      <c r="J164" s="7" t="s">
+      <c r="J143" s="4"/>
+    </row>
+    <row r="144" spans="1:11" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B144" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C144" s="28">
+        <v>1</v>
+      </c>
+      <c r="D144" s="28">
+        <v>1</v>
+      </c>
+      <c r="H144" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="J144" s="4"/>
+    </row>
+    <row r="145" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J145" s="4"/>
+    </row>
+    <row r="146" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J146" s="4"/>
+    </row>
+    <row r="147" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J147" s="4"/>
+    </row>
+    <row r="148" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J148" s="4"/>
+    </row>
+    <row r="149" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J149" s="4"/>
+    </row>
+    <row r="150" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J150" s="4"/>
+    </row>
+    <row r="151" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J151" s="4"/>
+    </row>
+    <row r="152" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J152" s="4"/>
+    </row>
+    <row r="153" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J153" s="4"/>
+    </row>
+    <row r="154" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J154" s="4"/>
+    </row>
+    <row r="155" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J155" s="4"/>
+    </row>
+    <row r="156" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J156" s="4"/>
+    </row>
+    <row r="157" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J157" s="4"/>
+    </row>
+    <row r="158" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J158" s="4"/>
+    </row>
+    <row r="159" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J159" s="4"/>
+    </row>
+    <row r="160" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J160" s="4"/>
+    </row>
+    <row r="161" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J161" s="4"/>
+    </row>
+    <row r="162" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J162" s="4"/>
+    </row>
+    <row r="163" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J163" s="4"/>
+    </row>
+    <row r="164" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J164" s="4" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="165" ht="15" customHeight="1" spans="10:10">
-      <c r="J165" s="7"/>
-    </row>
-    <row r="166" ht="15" customHeight="1" spans="10:10">
-      <c r="J166" s="7"/>
-    </row>
-    <row r="167" ht="15" customHeight="1" spans="10:10">
-      <c r="J167" s="7"/>
-    </row>
-    <row r="168" ht="15" customHeight="1" spans="10:10">
-      <c r="J168" s="7"/>
-    </row>
-    <row r="169" ht="15" customHeight="1" spans="10:10">
-      <c r="J169" s="7"/>
-    </row>
-    <row r="170" ht="15" customHeight="1" spans="10:10">
-      <c r="J170" s="7"/>
-    </row>
-    <row r="171" ht="15" customHeight="1" spans="10:10">
-      <c r="J171" s="7"/>
+    <row r="165" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J165" s="4"/>
+    </row>
+    <row r="166" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J166" s="4"/>
+    </row>
+    <row r="167" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J167" s="4"/>
+    </row>
+    <row r="168" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J168" s="4"/>
+    </row>
+    <row r="169" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J169" s="4"/>
+    </row>
+    <row r="170" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J170" s="4"/>
+    </row>
+    <row r="171" spans="10:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J171" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B143">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="B1:B143" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>